--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/aysen.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/aysen.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>10515.06</v>
+        <v>10404.95</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2264.49</v>
+        <v>2252.11</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1083.94</v>
+        <v>1082.56</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3655.85</v>
+        <v>3651.2</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>4026.98</v>
+        <v>4070.78</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2320.87</v>
+        <v>2328.5</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>4150.78</v>
+        <v>4222.43</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1360.85</v>
+        <v>1355.25</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>4315.65</v>
+        <v>4308.96</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2943.36</v>
+        <v>2958.56</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>21197.03</v>
+        <v>21306.5</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2754.27</v>
+        <v>2768.49</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>12069.83</v>
+        <v>11916.52</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2443.83</v>
+        <v>2412.78</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>5870.06</v>
+        <v>5795.49</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>7159.51</v>
+        <v>7144.02</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>6634.33</v>
+        <v>6619.97</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1881.56</v>
+        <v>1878.92</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>5242.06</v>
+        <v>5298.29</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>6759.16</v>
+        <v>6627.33</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>7526.73</v>
+        <v>7521.59</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2739.23</v>
+        <v>2780.93</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>6916.37</v>
+        <v>7084.56</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7929.79</v>
+        <v>8122.62</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>12453.54</v>
+        <v>12831.17</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>11130.43</v>
+        <v>11467.94</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>7785.61</v>
+        <v>8021.7</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2994.52</v>
+        <v>3009.99</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>828.25</v>
+        <v>832.52</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>10714.89</v>
+        <v>10744.31</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2998.85</v>
+        <v>3007.09</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1001.54</v>
+        <v>1010.65</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1207.44</v>
+        <v>1218.42</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>18498.52</v>
+        <v>18627.31</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2441.31</v>
+        <v>2458.31</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>13623.13</v>
+        <v>13609.08</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>5185.12</v>
+        <v>5179.77</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>3803.49</v>
+        <v>3776.25</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>857.28</v>
+        <v>851.14</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1720.93</v>
+        <v>1718.4</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>6987.06</v>
+        <v>6949.01</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>870.65</v>
+        <v>875.16</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>15131.49</v>
+        <v>15146.08</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2806.24</v>
+        <v>2930.17</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>3254.57</v>
+        <v>3349.11</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1074.41</v>
+        <v>1093.89</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>3869.69</v>
+        <v>3930.31</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>43111.19</v>
+        <v>43786.5</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1307.88</v>
+        <v>1307.81</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>11616.81</v>
+        <v>11616.21</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1880.93</v>
+        <v>1882.55</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>975.1799999999999</v>
+        <v>972.49</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>787.11</v>
+        <v>778.03</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2318.03</v>
+        <v>2304.71</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1713.8</v>
+        <v>1703.96</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1424.37</v>
+        <v>1391.22</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>10052.91</v>
+        <v>9788.18</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3443.06</v>
+        <v>3380.62</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>865.5</v>
+        <v>868.02</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1483.78</v>
+        <v>1502.04</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>9776.07</v>
+        <v>9903.639999999999</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>8430.459999999999</v>
+        <v>8540.469999999999</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1890.55</v>
+        <v>1937.08</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2247.98</v>
+        <v>2290.5</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>928.13</v>
+        <v>938.6900000000001</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>27279.37</v>
+        <v>27589.6</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>9316.76</v>
+        <v>9346.07</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1323.13</v>
+        <v>1328.61</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1105.23</v>
+        <v>1109.81</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>8593.17</v>
+        <v>8556.25</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>3065.49</v>
+        <v>3023.81</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2357.1</v>
+        <v>2369.79</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1613.11</v>
+        <v>1621.8</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1437.42</v>
+        <v>1442.87</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1579.07</v>
+        <v>1585.05</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1569.52</v>
+        <v>1565.55</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>8556.629999999999</v>
+        <v>8637.93</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>834.46</v>
+        <v>840.6799999999999</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>4080.51</v>
+        <v>4110.91</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1391.27</v>
+        <v>1388.11</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>8428.92</v>
+        <v>8409.790000000001</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>3033.72</v>
+        <v>3026.23</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>3377.84</v>
+        <v>3388.59</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>4277.93</v>
+        <v>4291.54</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1869.93</v>
+        <v>1879.87</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2891.89</v>
+        <v>2907.26</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>4726.36</v>
+        <v>4806.29</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>8438.950000000001</v>
+        <v>8296.370000000001</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>2567.03</v>
+        <v>2523.66</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>11835.85</v>
+        <v>11635.88</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>3722.49</v>
+        <v>3669.66</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>2473.52</v>
+        <v>2438.42</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>8302.84</v>
+        <v>8185</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>3250.84</v>
+        <v>3204.7</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>7190.18</v>
+        <v>7088.13</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>4261.21</v>
+        <v>4200.73</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1293.95</v>
+        <v>1276.17</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1914.62</v>
+        <v>1902.75</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2535.34</v>
+        <v>2583.55</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>835.8200000000001</v>
+        <v>851.71</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2218.12</v>
+        <v>2268.15</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>794.13</v>
+        <v>812.04</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>10381.13</v>
+        <v>10452.8</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1605.82</v>
+        <v>1584.43</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>7795.12</v>
+        <v>7679.63</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1072.5</v>
+        <v>1083.24</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2015.33</v>
+        <v>2023.18</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>4027.35</v>
+        <v>4053.61</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>2017.13</v>
+        <v>2021.76</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>4422.7</v>
+        <v>4432.84</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>4392.02</v>
+        <v>4402.09</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2166.27</v>
+        <v>2171.24</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1279.39</v>
+        <v>1287.95</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>10006.68</v>
+        <v>10073.66</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>773.16</v>
+        <v>778.34</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>888.4299999999999</v>
+        <v>894.38</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>977.85</v>
+        <v>984.4</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1274.19</v>
+        <v>1282.71</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>34079.07</v>
+        <v>34317.57</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>3661.8</v>
+        <v>3687.42</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>13592.77</v>
+        <v>13687.9</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>779.34</v>
+        <v>776.88</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>1343.15</v>
+        <v>1321.48</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1820.54</v>
+        <v>1791.16</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>775.6</v>
+        <v>763.17</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1481</v>
+        <v>1490.91</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/aysen.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M127"/>
+  <dimension ref="A1:M134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,22 +514,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1691-3125-CM25</t>
+          <t>2495-20-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-8-LR25</t>
+          <t>2239-9-LR22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,28 +569,28 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>10404.95</v>
+        <v>4906.83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>742-176-CM25</t>
+          <t>3171-22-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-8-LR25</t>
+          <t>2239-9-LR22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>61.102.094-5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,43 +630,43 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2252.11</v>
+        <v>4205.51</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>418-5470-CM25</t>
+          <t>3622-45-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2239-8-LR25</t>
+          <t>2239-9-LR22</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>69.253.500-6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>I MUNICIPALIDAD DE O HIGGINS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.041.579-0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,28 +691,28 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1082.56</v>
+        <v>2786.22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>854-364-CM25</t>
+          <t>854-246-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2239-8-LR25</t>
+          <t>2239-9-LR22</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,28 +752,28 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3651.2</v>
+        <v>11586.23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3951-360-CM25</t>
+          <t>854-250-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2239-8-LR25</t>
+          <t>2239-9-LR22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.974.700-3</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano Victor Domingo Silva</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,28 +813,28 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>4070.78</v>
+        <v>11062</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2713-1162-CM25</t>
+          <t>886182-231-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2239-8-LR25</t>
+          <t>2239-9-LR22</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>MULTI SAFE SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.751.057-8</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2328.5</v>
+        <v>2240.72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3949-406-CM25</t>
+          <t>3950-4621-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>4222.43</v>
+        <v>5775.71</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5575-192-CM25</t>
+          <t>1691-3125-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1355.25</v>
+        <v>10404.95</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2495-553-CM25</t>
+          <t>742-176-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>4308.96</v>
+        <v>2252.11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1691-3030-CM25</t>
+          <t>418-5470-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>DEEP FLY S.A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.419.925-1</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2958.56</v>
+        <v>1082.56</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>707426-206-CM25</t>
+          <t>854-364-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>21306.5</v>
+        <v>3651.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1691-3398-CM25</t>
+          <t>3951-360-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.974.700-3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>Consultorio General Urbano Victor Domingo Silva</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2768.49</v>
+        <v>4070.78</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1691-3311-CM25</t>
+          <t>2713-1162-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>11916.52</v>
+        <v>2328.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>854-382-CM25</t>
+          <t>3949-406-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2412.78</v>
+        <v>4222.43</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1691-3310-CM25</t>
+          <t>5575-192-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.888.569-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>5795.49</v>
+        <v>1355.25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>418-7318-CM25</t>
+          <t>2495-553-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>7144.02</v>
+        <v>4308.96</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3950-4858-CM25</t>
+          <t>1691-3030-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,27 +1500,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DEEP FLY S.A</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.419.925-1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>6619.97</v>
+        <v>2958.56</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1692-3035-CM25</t>
+          <t>707426-206-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CORCORAN Y COMPAÑIA SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>86.527.400-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1878.92</v>
+        <v>21306.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3949-475-CM25</t>
+          <t>1691-3398-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>5298.29</v>
+        <v>2768.49</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1691-3123-CM25</t>
+          <t>1691-3311-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>6627.33</v>
+        <v>11916.52</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3171-4-CM26</t>
+          <t>854-382-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.102.094-5</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE AYSEN</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>7521.59</v>
+        <v>2412.78</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1233615-15-CM26</t>
+          <t>1691-3310-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t xml:space="preserve">RODOLFO </t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>76.888.569-9</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2780.93</v>
+        <v>5795.49</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3791-49-CM26</t>
+          <t>3950-4858-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>7084.56</v>
+        <v>6619.97</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1079689-41-CM26</t>
+          <t>418-7318-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>8122.62</v>
+        <v>7144.02</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>886182-32-CM26</t>
+          <t>1692-3035-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>CORCORAN Y COMPAÑIA SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>86.527.400-9</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>12831.17</v>
+        <v>1878.92</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1691-167-CM26</t>
+          <t>3949-475-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>11467.94</v>
+        <v>5298.29</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1691-182-CM26</t>
+          <t>1691-3123-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>8021.7</v>
+        <v>6627.33</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1692-67-CM26</t>
+          <t>3171-4-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.102.094-5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>GOBERNACION MARITIMA DE AYSEN</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3009.99</v>
+        <v>7521.59</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1173435-8-CM26</t>
+          <t>1233615-15-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>73.182.900-4</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo XI Región</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>832.52</v>
+        <v>2780.93</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2713-173-CM26</t>
+          <t>1079689-41-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>10744.31</v>
+        <v>8122.62</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2713-171-CM26</t>
+          <t>3791-49-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3007.09</v>
+        <v>7084.56</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>418-218-CM26</t>
+          <t>1691-182-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1010.65</v>
+        <v>8021.7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2713-185-CM26</t>
+          <t>1691-167-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1218.42</v>
+        <v>11467.94</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>707426-13-CM26</t>
+          <t>886182-32-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Universidad de Aysen</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>18627.31</v>
+        <v>12831.17</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1428-8-CM26</t>
+          <t>1692-67-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.701.004-8</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2458.31</v>
+        <v>3009.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>951405-33-CM26</t>
+          <t>1173435-8-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>73.182.900-4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>Centro de Educación y Trabajo XI Región</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>13609.08</v>
+        <v>832.52</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2713-211-CM26</t>
+          <t>2713-171-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>5179.77</v>
+        <v>3007.09</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1691-271-CM26</t>
+          <t>2713-173-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>DEEP FLY S.A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.419.925-1</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>3776.25</v>
+        <v>10744.31</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1403-93-CM26</t>
+          <t>418-218-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>851.14</v>
+        <v>1010.65</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>930039-11-CM26</t>
+          <t>2713-185-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1718.4</v>
+        <v>1218.42</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>734-51-CM26</t>
+          <t>707426-13-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>6949.01</v>
+        <v>18627.31</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2500-33-CM26</t>
+          <t>1428-8-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>60.701.004-8</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>Servicio Nacional de Pesca y Acuicultura</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>875.16</v>
+        <v>2458.31</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1274667-81-CM26</t>
+          <t>951405-33-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>15146.08</v>
+        <v>13609.08</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1691-348-CM26</t>
+          <t>2713-211-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2930.17</v>
+        <v>5179.77</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2495-45-CM26</t>
+          <t>1691-271-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DEEP FLY S.A</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.419.925-1</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>3349.11</v>
+        <v>3776.25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>854-25-CM26</t>
+          <t>1403-93-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1093.89</v>
+        <v>851.14</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3950-294-CM26</t>
+          <t>930039-11-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>Servicio Nacional del Patrimonio Cultural</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>3930.31</v>
+        <v>1718.4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>854-28-CM26</t>
+          <t>734-51-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>43786.5</v>
+        <v>6949.01</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2713-292-CM26</t>
+          <t>2500-33-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1307.81</v>
+        <v>875.16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4778-88-CM26</t>
+          <t>1274667-81-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>11616.21</v>
+        <v>15146.08</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>749-7-CM26</t>
+          <t>1691-348-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1882.55</v>
+        <v>2930.17</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3950-397-CM26</t>
+          <t>2495-45-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>972.49</v>
+        <v>3349.11</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1403-177-CM26</t>
+          <t>854-25-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>778.03</v>
+        <v>1093.89</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>418-814-CM26</t>
+          <t>3950-294-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2304.71</v>
+        <v>3930.31</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>418-904-CM26</t>
+          <t>854-28-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1703.96</v>
+        <v>43786.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3949-128-CM26</t>
+          <t>2713-292-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1391.22</v>
+        <v>1307.81</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4778-140-CM26</t>
+          <t>4778-88-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>9788.18</v>
+        <v>11616.21</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2713-386-CM26</t>
+          <t>749-7-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3380.62</v>
+        <v>1882.55</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2042-118-CM26</t>
+          <t>3950-397-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4062,27 +4062,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.253.400-k</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TORTEL</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>868.02</v>
+        <v>972.49</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1426103-32-CM26</t>
+          <t>1403-177-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1502.04</v>
+        <v>778.03</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4778-201-CM26</t>
+          <t>418-814-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.888.569-9</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>9903.639999999999</v>
+        <v>2304.71</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>418-1220-CM26</t>
+          <t>418-904-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>8540.469999999999</v>
+        <v>1703.96</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>951405-108-CM26</t>
+          <t>3949-128-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>LOGISTRA SPA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>78.209.481-5</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1937.08</v>
+        <v>1391.22</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2713-436-CM26</t>
+          <t>4778-140-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2290.5</v>
+        <v>9788.18</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2500-70-CM26</t>
+          <t>2713-386-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>938.6900000000001</v>
+        <v>3380.62</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4778-217-CM26</t>
+          <t>2042-118-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4494,22 +4494,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.253.400-k</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE TORTEL</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>27589.6</v>
+        <v>868.02</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4778-231-CM26</t>
+          <t>1426103-32-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>EQUILIBRIUM SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.475.342-9</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>9346.07</v>
+        <v>1502.04</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4778-236-CM26</t>
+          <t>4778-201-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1328.61</v>
+        <v>9903.639999999999</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>611136-13-CM26</t>
+          <t>418-1220-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,22 +4677,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.979.930-5</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1109.81</v>
+        <v>8540.469999999999</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>868-57-CM26</t>
+          <t>951405-108-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>72.222.000-5</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE AYSEN</t>
+          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>MAKRON CHILE SPA</t>
+          <t>LOGISTRA SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>78.209.499-8</t>
+          <t>78.209.481-5</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>8556.25</v>
+        <v>1937.08</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1691-919-CM26</t>
+          <t>2713-436-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>DEEP FLY S.A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.419.925-1</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>3023.81</v>
+        <v>2290.5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>418-1399-CM26</t>
+          <t>2500-70-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>EQUILIBRIUM SPA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.475.342-9</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2369.79</v>
+        <v>938.6900000000001</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>418-1467-CM26</t>
+          <t>4778-217-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4916,12 +4916,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1621.8</v>
+        <v>27589.6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>951405-139-CM26</t>
+          <t>4778-231-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4977,12 +4977,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1442.87</v>
+        <v>9346.07</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2713-523-CM26</t>
+          <t>4778-236-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t xml:space="preserve">RODOLFO </t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>76.888.569-9</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1585.05</v>
+        <v>1328.61</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1692-320-CM26</t>
+          <t>611136-13-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5099,27 +5099,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.979.930-5</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1565.55</v>
+        <v>1109.81</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1079689-185-CM26</t>
+          <t>868-57-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>72.222.000-5</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>GOBIERNO REGIONAL DE AYSEN</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>MAKRON CHILE SPA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>78.209.499-8</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>8637.93</v>
+        <v>8556.25</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3949-192-CM26</t>
+          <t>1691-919-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DEEP FLY S.A</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.419.925-1</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>840.6799999999999</v>
+        <v>3023.81</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3765-420-CM26</t>
+          <t>418-1399-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>4110.91</v>
+        <v>2369.79</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>951405-168-CM26</t>
+          <t>418-1467-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1388.11</v>
+        <v>1621.8</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>951405-169-CM26</t>
+          <t>951405-139-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>8409.790000000001</v>
+        <v>1442.87</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2495-204-CM26</t>
+          <t>2713-523-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>3026.23</v>
+        <v>1585.05</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4778-309-CM26</t>
+          <t>1692-320-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>76.888.569-9</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>3388.59</v>
+        <v>1565.55</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>854-90-CM26</t>
+          <t>1079689-185-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>4291.54</v>
+        <v>8637.93</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>418-1749-CM26</t>
+          <t>3765-420-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1879.87</v>
+        <v>4110.91</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>418-1750-CM26</t>
+          <t>3949-192-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>AVA COMERCIAL SPA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>78.203.286-0</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2907.26</v>
+        <v>840.6799999999999</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>418-1800-CM26</t>
+          <t>951405-168-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>4806.29</v>
+        <v>1388.11</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4778-313-CM26</t>
+          <t>951405-169-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>CORCORAN Y COMPAÑIA SPA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>86.527.400-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>8296.370000000001</v>
+        <v>8409.790000000001</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4778-326-CM26</t>
+          <t>2495-204-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>2523.66</v>
+        <v>3026.23</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>707426-91-CM26</t>
+          <t>4778-309-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t xml:space="preserve">RODOLFO </t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.888.569-9</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>11635.88</v>
+        <v>3388.59</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3950-855-CM26</t>
+          <t>854-90-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>3669.66</v>
+        <v>4291.54</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3950-838-CM26</t>
+          <t>418-1749-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6075,12 +6075,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>2438.42</v>
+        <v>1879.87</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3950-854-CM26</t>
+          <t>418-1750-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>AVA COMERCIAL SPA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>78.203.286-0</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>8185</v>
+        <v>2907.26</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3949-225-CM26</t>
+          <t>418-1800-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>3204.7</v>
+        <v>4806.29</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1691-1199-CM26</t>
+          <t>4778-313-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>DEEP FLY S.A</t>
+          <t>CORCORAN Y COMPAÑIA SPA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>76.419.925-1</t>
+          <t>86.527.400-9</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>7088.13</v>
+        <v>8296.370000000001</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3951-130-CM26</t>
+          <t>4778-326-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.974.700-3</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano Victor Domingo Silva</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>4200.73</v>
+        <v>2523.66</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>418-1927-CM26</t>
+          <t>707426-91-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1276.17</v>
+        <v>11635.88</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>697209-13-CM26</t>
+          <t>3950-855-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6446,22 +6446,22 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1902.75</v>
+        <v>3669.66</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>707426-97-CM26</t>
+          <t>3950-854-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6507,22 +6507,22 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2583.55</v>
+        <v>8185</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>854-106-CM26</t>
+          <t>3950-838-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>851.71</v>
+        <v>2438.42</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>418-2007-CM26</t>
+          <t>3951-130-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.974.700-3</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>Consultorio General Urbano Victor Domingo Silva</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2268.15</v>
+        <v>4200.73</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>854-109-CM26</t>
+          <t>3949-225-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>812.04</v>
+        <v>3204.7</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1274667-215-CM26</t>
+          <t>1691-1199-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DEEP FLY S.A</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.419.925-1</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>10452.8</v>
+        <v>7088.13</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2713-690-CM26</t>
+          <t>418-1927-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6812,7 +6812,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6822,12 +6822,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1584.43</v>
+        <v>1276.17</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1426103-59-CM26</t>
+          <t>697209-13-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>7679.63</v>
+        <v>1902.75</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>3949-271-CM26</t>
+          <t>707426-97-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6929,27 +6929,27 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1083.24</v>
+        <v>2583.55</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2713-736-CM26</t>
+          <t>854-106-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6990,27 +6990,27 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2023.18</v>
+        <v>851.71</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>734-474-CM26</t>
+          <t>418-2007-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7051,27 +7051,27 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>4053.61</v>
+        <v>2268.15</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>418-2205-CM26</t>
+          <t>854-109-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7112,12 +7112,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>2021.76</v>
+        <v>812.04</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>3949-279-CM26</t>
+          <t>1274667-215-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>4432.84</v>
+        <v>10452.8</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>418-2204-CM26</t>
+          <t>2713-690-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>AVA COMERCIAL SPA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>78.203.286-0</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>4402.09</v>
+        <v>1584.43</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1079689-279-CM26</t>
+          <t>1426103-59-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7295,27 +7295,27 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2171.24</v>
+        <v>7679.63</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1274667-235-CM26</t>
+          <t>3949-271-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7361,22 +7361,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1287.95</v>
+        <v>1083.24</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1274667-237-CM26</t>
+          <t>2713-736-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>10073.66</v>
+        <v>2023.18</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1274667-258-CM26</t>
+          <t>734-474-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>778.34</v>
+        <v>4053.61</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1274667-263-CM26</t>
+          <t>3949-279-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7544,22 +7544,22 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>894.38</v>
+        <v>4432.84</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1692-459-CM26</t>
+          <t>418-2205-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7605,22 +7605,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7645,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>984.4</v>
+        <v>2021.76</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1692-460-CM26</t>
+          <t>418-2204-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7676,12 +7676,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>AVA COMERCIAL SPA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>78.203.286-0</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1282.71</v>
+        <v>4402.09</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>4778-405-CM26</t>
+          <t>1079689-279-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>34317.57</v>
+        <v>2171.24</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>4778-406-CM26</t>
+          <t>1274667-235-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7788,22 +7788,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7813,12 +7813,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>3687.42</v>
+        <v>1287.95</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>4778-407-CM26</t>
+          <t>1274667-237-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7849,22 +7849,22 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7874,12 +7874,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>13687.9</v>
+        <v>10073.66</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>3765-630-CM26</t>
+          <t>1274667-258-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7910,22 +7910,22 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>776.88</v>
+        <v>778.34</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1403-461-CM26</t>
+          <t>1274667-263-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>1321.48</v>
+        <v>894.38</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>967384-3-CM26</t>
+          <t>1692-459-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.999.100-1</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ejército de Chile</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1791.16</v>
+        <v>984.4</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1403-574-CM26</t>
+          <t>1692-460-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>763.17</v>
+        <v>1282.71</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2151-286-CM26</t>
+          <t>4778-405-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8154,22 +8154,22 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8194,6 +8194,433 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
+        <v>34317.57</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>4778-406-CM26</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>3687.42</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>4778-407-CM26</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>13687.9</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>3765-630-CM26</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>61.602.281-4</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>776.88</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>1403-461-CM26</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>61.004.101-9</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>1321.48</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>967384-3-CM26</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>61.999.100-1</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Ejército de Chile</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>1791.16</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>1403-574-CM26</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>61.004.101-9</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>763.17</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2151-286-CM26</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>61.602.293-8</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="n">
         <v>1490.91</v>
       </c>
     </row>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/aysen.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M254"/>
+  <dimension ref="A1:M269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1002,7 +1002,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1691-138-CM25</t>
+          <t>3950-831-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2219.13</v>
+        <v>4246.66</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3950-831-CM25</t>
+          <t>1691-138-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1083,17 +1083,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4246.66</v>
+        <v>2219.13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>742-5-CM25</t>
+          <t>2495-20-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2332.86</v>
+        <v>4906.83</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2495-20-CM25</t>
+          <t>742-5-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4906.83</v>
+        <v>2332.86</v>
       </c>
     </row>
     <row r="14">
@@ -1795,7 +1795,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>418-630-CM25</t>
+          <t>1691-638-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>CORCORAN Y COMPAÑIA SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>86.527.400-9</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2458.01</v>
+        <v>3242.22</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1691-641-CM25</t>
+          <t>1691-637-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>5304.14</v>
+        <v>16579.02</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1691-638-CM25</t>
+          <t>1691-641-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>CORCORAN Y COMPAÑIA SPA</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>86.527.400-9</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>3242.22</v>
+        <v>5304.14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1691-637-CM25</t>
+          <t>418-630-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>16579.02</v>
+        <v>2458.01</v>
       </c>
     </row>
     <row r="27">
@@ -2954,7 +2954,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1691-1170-CM25</t>
+          <t>1691-1166-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>DEEP FLY S.A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.419.925-1</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2115.37</v>
+        <v>3185.98</v>
       </c>
     </row>
     <row r="43">
@@ -3076,7 +3076,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1691-1166-CM25</t>
+          <t>1691-1170-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DEEP FLY S.A</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.419.925-1</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3185.98</v>
+        <v>2115.37</v>
       </c>
     </row>
     <row r="45">
@@ -3503,7 +3503,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>854-94-CM25</t>
+          <t>1691-1364-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>6520.2</v>
+        <v>2667.41</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1691-1364-CM25</t>
+          <t>854-96-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>JOHANA JESSICA ROJAS BOUFFANAIS</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>11.297.949-2</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2667.41</v>
+        <v>3656.48</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>854-96-CM25</t>
+          <t>854-94-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>JOHANA JESSICA ROJAS BOUFFANAIS</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>11.297.949-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>3656.48</v>
+        <v>6520.2</v>
       </c>
     </row>
     <row r="54">
@@ -4174,7 +4174,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1691-1622-CM25</t>
+          <t>1691-1689-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>WINKLER LIMITADA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>79.722.860-5</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2354.27</v>
+        <v>3235.45</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1691-1689-CM25</t>
+          <t>1691-1622-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>WINKLER LIMITADA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>79.722.860-5</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>3235.45</v>
+        <v>2354.27</v>
       </c>
     </row>
     <row r="64">
@@ -4357,7 +4357,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1691-1552-CM25</t>
+          <t>1691-1791-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>HIMAX</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.199.800-5</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>4168.86</v>
+        <v>3846.84</v>
       </c>
     </row>
     <row r="66">
@@ -4479,7 +4479,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1691-1791-CM25</t>
+          <t>1691-1552-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>HIMAX</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.199.800-5</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>3846.84</v>
+        <v>4168.86</v>
       </c>
     </row>
     <row r="68">
@@ -4723,7 +4723,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2713-600-CM25</t>
+          <t>3622-45-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4743,17 +4743,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>69.253.500-6</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>I MUNICIPALIDAD DE O HIGGINS</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>4375.82</v>
+        <v>2786.22</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3950-3933-CM25</t>
+          <t>2713-600-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4804,17 +4804,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>76.041.579-0</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2980.39</v>
+        <v>4375.82</v>
       </c>
     </row>
     <row r="73">
@@ -4906,7 +4906,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3622-45-CM25</t>
+          <t>3950-3933-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.253.500-6</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE O HIGGINS</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.041.579-0</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2786.22</v>
+        <v>2980.39</v>
       </c>
     </row>
     <row r="75">
@@ -5028,7 +5028,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1004-159-CM25</t>
+          <t>1691-1956-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5048,17 +5048,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2582.96</v>
+        <v>15331.92</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1691-1956-CM25</t>
+          <t>1004-159-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5109,17 +5109,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>15331.92</v>
+        <v>2582.96</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>854-247-CM25</t>
+          <t>854-246-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>3083</v>
+        <v>11586.23</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>854-246-CM25</t>
+          <t>854-247-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>11586.23</v>
+        <v>3083</v>
       </c>
     </row>
     <row r="80">
@@ -5699,7 +5699,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3949-309-CM25</t>
+          <t>3951-260-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.974.700-3</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>ethos</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>78.583.750-9</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>4104.96</v>
+        <v>2871.56</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3951-260-CM25</t>
+          <t>3949-309-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.974.700-3</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>ethos</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>78.583.750-9</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2871.56</v>
+        <v>4104.96</v>
       </c>
     </row>
     <row r="89">
@@ -6858,7 +6858,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>854-337-CM25</t>
+          <t>854-338-CM25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>4925.87</v>
+        <v>2604.88</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>854-338-CM25</t>
+          <t>854-337-CM25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2604.88</v>
+        <v>4925.87</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>3950-4621-CM25</t>
+          <t>3950-4619-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>5775.71</v>
+        <v>5123.14</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3950-4619-CM25</t>
+          <t>3950-4621-CM25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>5123.14</v>
+        <v>5775.71</v>
       </c>
     </row>
     <row r="110">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano Victor Domingo Silva</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE AYSEN</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8444,7 +8444,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3791-49-CM26</t>
+          <t>1079689-41-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>7084.56</v>
+        <v>8122.62</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1079689-41-CM26</t>
+          <t>3791-49-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8560,13 +8560,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>8122.62</v>
+        <v>7084.56</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>886182-32-CM26</t>
+          <t>1691-182-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>12831.17</v>
+        <v>8021.7</v>
       </c>
     </row>
     <row r="135">
@@ -8688,7 +8688,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1691-182-CM26</t>
+          <t>886182-32-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>8021.7</v>
+        <v>12831.17</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1173435-8-CM26</t>
+          <t>1692-67-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>73.182.900-4</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo XI Región</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>832.52</v>
+        <v>3009.99</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1692-67-CM26</t>
+          <t>1173435-8-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>73.182.900-4</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>3009.99</v>
+        <v>832.52</v>
       </c>
     </row>
     <row r="139">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9359,7 +9359,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1403-93-CM26</t>
+          <t>1691-271-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9384,12 +9384,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9399,12 +9399,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DEEP FLY S.A</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.419.925-1</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -9414,13 +9414,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>851.14</v>
+        <v>3776.25</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1691-271-CM26</t>
+          <t>1403-93-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>DEEP FLY S.A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>76.419.925-1</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>3776.25</v>
+        <v>851.14</v>
       </c>
     </row>
     <row r="149">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9908,7 +9908,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>854-28-CM26</t>
+          <t>3950-294-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9963,13 +9963,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>43786.5</v>
+        <v>3930.31</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3950-294-CM26</t>
+          <t>854-28-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>3930.31</v>
+        <v>43786.5</v>
       </c>
     </row>
     <row r="158">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TORTEL</t>
+          <t>Ilustre Municipalidad de Tortel</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11046,7 +11046,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -11585,7 +11585,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -12226,7 +12226,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>418-1750-CM26</t>
+          <t>418-1749-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12266,12 +12266,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>AVA COMERCIAL SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>78.203.286-0</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -12281,13 +12281,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>2907.26</v>
+        <v>1879.87</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>418-1749-CM26</t>
+          <t>418-1750-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12327,12 +12327,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>AVA COMERCIAL SPA</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>78.203.286-0</t>
         </is>
       </c>
       <c r="K195" t="inlineStr"/>
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>1879.87</v>
+        <v>2907.26</v>
       </c>
     </row>
     <row r="196">
@@ -12592,7 +12592,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>3950-854-CM26</t>
+          <t>3950-855-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K200" t="inlineStr"/>
@@ -12647,13 +12647,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>8185</v>
+        <v>3669.66</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>3950-855-CM26</t>
+          <t>3950-854-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>3669.66</v>
+        <v>8185</v>
       </c>
     </row>
     <row r="202">
@@ -12775,7 +12775,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>3949-225-CM26</t>
+          <t>3951-130-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12800,12 +12800,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.974.700-3</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12830,13 +12830,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>3204.7</v>
+        <v>4200.73</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1691-1199-CM26</t>
+          <t>3949-225-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12861,12 +12861,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12876,12 +12876,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>DEEP FLY S.A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>76.419.925-1</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
@@ -12891,13 +12891,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>7088.13</v>
+        <v>3204.7</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>3951-130-CM26</t>
+          <t>1691-1199-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>61.974.700-3</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano Victor Domingo Silva</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -12937,12 +12937,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DEEP FLY S.A</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.419.925-1</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>4200.73</v>
+        <v>7088.13</v>
       </c>
     </row>
     <row r="206">
@@ -13100,7 +13100,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -13202,7 +13202,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>854-109-CM26</t>
+          <t>418-2007-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13227,12 +13227,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13242,12 +13242,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K210" t="inlineStr"/>
@@ -13257,13 +13257,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>812.04</v>
+        <v>2268.15</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>418-2007-CM26</t>
+          <t>854-109-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13288,12 +13288,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13303,12 +13303,12 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K211" t="inlineStr"/>
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>2268.15</v>
+        <v>812.04</v>
       </c>
     </row>
     <row r="212">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -13690,7 +13690,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1079689-279-CM26</t>
+          <t>3949-279-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13715,12 +13715,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13730,12 +13730,12 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K218" t="inlineStr"/>
@@ -13745,13 +13745,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>2171.24</v>
+        <v>4432.84</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>418-2204-CM26</t>
+          <t>418-2205-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>AVA COMERCIAL SPA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>78.203.286-0</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K219" t="inlineStr"/>
@@ -13806,13 +13806,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>4402.09</v>
+        <v>2021.76</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>418-2205-CM26</t>
+          <t>418-2204-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13852,12 +13852,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>AVA COMERCIAL SPA</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>78.203.286-0</t>
         </is>
       </c>
       <c r="K220" t="inlineStr"/>
@@ -13867,13 +13867,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>2021.76</v>
+        <v>4402.09</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>3949-279-CM26</t>
+          <t>1079689-279-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13898,12 +13898,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -13913,12 +13913,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -13928,13 +13928,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>4432.84</v>
+        <v>2171.24</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1692-460-CM26</t>
+          <t>1274667-235-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13959,12 +13959,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -13974,12 +13974,12 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K222" t="inlineStr"/>
@@ -13989,13 +13989,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>1282.71</v>
+        <v>1287.95</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1692-459-CM26</t>
+          <t>1274667-237-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14015,17 +14015,17 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14035,12 +14035,12 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
@@ -14050,13 +14050,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>984.4</v>
+        <v>10073.66</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1274667-263-CM26</t>
+          <t>1274667-258-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -14096,12 +14096,12 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K224" t="inlineStr"/>
@@ -14111,13 +14111,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>894.38</v>
+        <v>778.34</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1274667-237-CM26</t>
+          <t>1274667-263-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14137,7 +14137,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -14157,12 +14157,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K225" t="inlineStr"/>
@@ -14172,13 +14172,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>10073.66</v>
+        <v>894.38</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1274667-235-CM26</t>
+          <t>1692-459-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14198,17 +14198,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14218,12 +14218,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K226" t="inlineStr"/>
@@ -14233,13 +14233,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>1287.95</v>
+        <v>984.4</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1274667-258-CM26</t>
+          <t>1692-460-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14259,17 +14259,17 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>778.34</v>
+        <v>1282.71</v>
       </c>
     </row>
     <row r="228">
@@ -14544,7 +14544,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>967384-3-CM26</t>
+          <t>1403-461-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14564,17 +14564,17 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>61.999.100-1</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Ejército de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14599,13 +14599,13 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>1791.16</v>
+        <v>1321.48</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1403-461-CM26</t>
+          <t>967384-3-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -14625,17 +14625,17 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.999.100-1</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>1321.48</v>
+        <v>1791.16</v>
       </c>
     </row>
     <row r="234">
@@ -14696,7 +14696,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -15276,7 +15276,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>418-2658-CM26</t>
+          <t>3171-140-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15301,12 +15301,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.102.094-5</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15316,12 +15316,12 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
@@ -15331,13 +15331,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>4912.07</v>
+        <v>1225.59</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2151-315-CM26</t>
+          <t>707426-116-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15392,13 +15392,13 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>1524.83</v>
+        <v>2988.45</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>707426-116-CM26</t>
+          <t>2151-315-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15423,12 +15423,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15453,13 +15453,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>2988.45</v>
+        <v>1524.83</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>3171-140-CM26</t>
+          <t>418-2658-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15484,12 +15484,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>61.102.094-5</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15499,12 +15499,12 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K247" t="inlineStr"/>
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>1225.59</v>
+        <v>4912.07</v>
       </c>
     </row>
     <row r="248">
@@ -15540,7 +15540,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -15703,7 +15703,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>418-2662-CM26</t>
+          <t>418-2753-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -15743,12 +15743,12 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>AVA COMERCIAL SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>78.203.286-0</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
@@ -15758,13 +15758,13 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>5464.05</v>
+        <v>1274.88</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>418-2753-CM26</t>
+          <t>418-2763-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -15819,13 +15819,13 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>1274.88</v>
+        <v>3054.33</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>418-2763-CM26</t>
+          <t>418-2662-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -15845,7 +15845,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>AVA COMERCIAL SPA</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>78.203.286-0</t>
         </is>
       </c>
       <c r="K253" t="inlineStr"/>
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>3054.33</v>
+        <v>5464.05</v>
       </c>
     </row>
     <row r="254">
@@ -15942,6 +15942,921 @@
       </c>
       <c r="M254" s="2" t="n">
         <v>1089.48</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>1426103-82-CM26</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M255" s="2" t="n">
+        <v>1878.69</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>3765-780-CM26</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>61.602.281-4</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr"/>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M256" s="2" t="n">
+        <v>2447.53</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2713-995-CM26</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M257" s="2" t="n">
+        <v>995.9</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>3949-368-CM26</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>61.974.500-0</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M258" s="2" t="n">
+        <v>2940.69</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2713-1004-CM26</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M259" s="2" t="n">
+        <v>2386.82</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>4778-570-CM26</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M260" s="2" t="n">
+        <v>3233.41</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>3951-257-CM26</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>61.974.700-3</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M261" s="2" t="n">
+        <v>2474.99</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>1692-645-CM26</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>61.602.292-k</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M262" s="2" t="n">
+        <v>2613.53</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>3950-1463-CM26</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>61.974.600-7</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>DIRECCION SALUD RURAL</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M263" s="2" t="n">
+        <v>7710.47</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>3950-1465-CM26</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>61.974.600-7</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>DIRECCION SALUD RURAL</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M264" s="2" t="n">
+        <v>3055.08</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>886182-303-CM26</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>61.980.520-8</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M265" s="2" t="n">
+        <v>2282.11</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2713-1071-CM26</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M266" s="2" t="n">
+        <v>1681.83</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>742-91-CM26</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>61.307.000-1</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M267" s="2" t="n">
+        <v>1404.27</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>418-3085-CM26</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>61.602.279-2</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M268" s="2" t="n">
+        <v>1637.21</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>4778-575-CM26</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M269" s="2" t="n">
+        <v>1644.47</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/aysen.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/aysen.xlsx
@@ -562,7 +562,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1005,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1253,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1318,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1383,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1448,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1635,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1700,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1765,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1830,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2017,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2204,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2452,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2578,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2704,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2769,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3017,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3387,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3757,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +3944,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4070,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4135,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4322,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5058,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5245,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5371,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5497,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6111,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6298,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6363,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +6916,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7042,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7107,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7416,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7481,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7729,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +7977,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8530,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8656,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8721,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +8908,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9095,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9160,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9347,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9412,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9477,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9542,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +9729,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +9794,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +9859,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10107,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10477,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +10908,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11156,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11221,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11530,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11595,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12209,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +12518,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12583,11 @@
           <t>78.203.286-0</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12648,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13384,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13510,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +13758,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +13945,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14132,11 @@
           <t>78.203.286-0</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14258,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14445,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +14510,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +14758,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +14884,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +14949,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15014,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15201,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +15571,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +15636,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +15701,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +15766,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +15892,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +15957,11 @@
           <t>77.884.798-1</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16083,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16148,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16213,11 @@
           <t>78.203.286-0</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +16339,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17014,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17140,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17205,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/aysen.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/aysen.xlsx
@@ -1070,7 +1070,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5310,7 +5314,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9225,7 +9233,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10416,7 +10428,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13575,7 +13591,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/aysen.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M269"/>
+  <dimension ref="A1:M279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8933,7 +8933,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1692-67-CM26</t>
+          <t>1173435-8-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>73.182.900-4</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8988,13 +8988,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>3009.99</v>
+        <v>832.52</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1173435-8-CM26</t>
+          <t>1692-67-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9019,12 +9019,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>73.182.900-4</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9049,13 +9049,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>832.52</v>
+        <v>3009.99</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2713-171-CM26</t>
+          <t>2713-173-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9114,13 +9114,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>3007.09</v>
+        <v>10744.31</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2713-173-CM26</t>
+          <t>2713-171-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9179,13 +9179,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>10744.31</v>
+        <v>3007.09</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>418-218-CM26</t>
+          <t>2713-185-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9210,12 +9210,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9225,32 +9225,28 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1010.65</v>
+        <v>1218.42</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2713-185-CM26</t>
+          <t>418-218-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9275,12 +9271,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9290,22 +9286,26 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr"/>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>1218.42</v>
+        <v>1010.65</v>
       </c>
     </row>
     <row r="143">
@@ -9441,7 +9441,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>951405-33-CM26</t>
+          <t>2713-211-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9500,13 +9500,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>13609.08</v>
+        <v>5179.77</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2713-211-CM26</t>
+          <t>951405-33-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9565,13 +9565,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>5179.77</v>
+        <v>13609.08</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1691-271-CM26</t>
+          <t>1403-93-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>DEEP FLY S.A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>76.419.925-1</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -9626,13 +9626,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>3776.25</v>
+        <v>851.14</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1403-93-CM26</t>
+          <t>1691-271-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DEEP FLY S.A</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.419.925-1</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -9687,7 +9687,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>851.14</v>
+        <v>3776.25</v>
       </c>
     </row>
     <row r="149">
@@ -10136,7 +10136,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>3950-294-CM26</t>
+          <t>854-28-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10191,13 +10191,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>3930.31</v>
+        <v>43786.5</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>854-28-CM26</t>
+          <t>3950-294-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>43786.5</v>
+        <v>3930.31</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2713-292-CM26</t>
+          <t>4778-88-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10283,12 +10283,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10298,12 +10298,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10313,13 +10313,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>1307.81</v>
+        <v>11616.21</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>4778-88-CM26</t>
+          <t>2713-292-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10344,12 +10344,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10374,7 +10374,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>11616.21</v>
+        <v>1307.81</v>
       </c>
     </row>
     <row r="160">
@@ -10571,7 +10571,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>418-814-CM26</t>
+          <t>418-904-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10626,13 +10626,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>2304.71</v>
+        <v>1703.96</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>418-904-CM26</t>
+          <t>418-814-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1703.96</v>
+        <v>2304.71</v>
       </c>
     </row>
     <row r="165">
@@ -11002,7 +11002,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>4778-201-CM26</t>
+          <t>418-1220-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11027,12 +11027,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rodolfo </t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>76.888.569-9</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -11057,13 +11057,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>9903.639999999999</v>
+        <v>8540.469999999999</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>418-1220-CM26</t>
+          <t>4778-201-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11088,12 +11088,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.888.569-9</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -11118,7 +11118,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>8540.469999999999</v>
+        <v>9903.639999999999</v>
       </c>
     </row>
     <row r="172">
@@ -11254,7 +11254,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2500-70-CM26</t>
+          <t>4778-217-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11279,12 +11279,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11294,12 +11294,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Equilibrium SpA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -11309,13 +11309,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>938.6900000000001</v>
+        <v>27589.6</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>4778-217-CM26</t>
+          <t>2500-70-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11355,12 +11355,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.475.342-9</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -11370,7 +11370,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>27589.6</v>
+        <v>938.6900000000001</v>
       </c>
     </row>
     <row r="176">
@@ -11437,7 +11437,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>4778-236-CM26</t>
+          <t>611136-13-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11457,17 +11457,17 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.979.930-5</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11477,28 +11477,32 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rodolfo </t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>76.888.569-9</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr"/>
+          <t>77.806.000-0</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>1328.61</v>
+        <v>1109.81</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>611136-13-CM26</t>
+          <t>4778-236-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11518,17 +11522,17 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>61.979.930-5</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11538,26 +11542,22 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.888.569-9</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>1109.81</v>
+        <v>1328.61</v>
       </c>
     </row>
     <row r="179">
@@ -12055,7 +12055,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>3765-420-CM26</t>
+          <t>3949-192-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -12110,13 +12110,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>4110.91</v>
+        <v>840.6799999999999</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>3949-192-CM26</t>
+          <t>3765-420-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12171,13 +12171,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>840.6799999999999</v>
+        <v>4110.91</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>951405-168-CM26</t>
+          <t>951405-169-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12217,32 +12217,28 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>1388.11</v>
+        <v>8409.790000000001</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>951405-169-CM26</t>
+          <t>951405-168-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12282,22 +12278,26 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>8409.790000000001</v>
+        <v>1388.11</v>
       </c>
     </row>
     <row r="191">
@@ -12486,7 +12486,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>418-1749-CM26</t>
+          <t>418-1750-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12526,12 +12526,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>AVA COMERCIAL SPA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>78.203.286-0</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -12545,13 +12545,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>1879.87</v>
+        <v>2907.26</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>418-1750-CM26</t>
+          <t>418-1749-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12591,12 +12591,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>AVA COMERCIAL SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>78.203.286-0</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -12610,7 +12610,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>2907.26</v>
+        <v>1879.87</v>
       </c>
     </row>
     <row r="196">
@@ -12681,7 +12681,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>4778-313-CM26</t>
+          <t>707426-91-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12706,12 +12706,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12721,12 +12721,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>CORCORAN Y COMPAÑIA SPA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>86.527.400-9</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
@@ -12736,7 +12736,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>8296.370000000001</v>
+        <v>11635.88</v>
       </c>
     </row>
     <row r="198">
@@ -12803,7 +12803,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>707426-91-CM26</t>
+          <t>4778-313-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>CORCORAN Y COMPAÑIA SPA</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>86.527.400-9</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -12858,13 +12858,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>11635.88</v>
+        <v>8296.370000000001</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>3950-855-CM26</t>
+          <t>3950-854-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12904,12 +12904,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K200" t="inlineStr"/>
@@ -12919,13 +12919,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>3669.66</v>
+        <v>8185</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>3950-854-CM26</t>
+          <t>3950-838-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12980,13 +12980,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>8185</v>
+        <v>2438.42</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>3950-838-CM26</t>
+          <t>3951-130-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -13011,12 +13011,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.974.700-3</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -13041,13 +13041,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>2438.42</v>
+        <v>4200.73</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>3951-130-CM26</t>
+          <t>1691-1199-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13072,12 +13072,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>61.974.700-3</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -13087,12 +13087,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DEEP FLY S.A</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.419.925-1</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
@@ -13102,7 +13102,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>4200.73</v>
+        <v>7088.13</v>
       </c>
     </row>
     <row r="204">
@@ -13169,7 +13169,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1691-1199-CM26</t>
+          <t>3950-855-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13194,12 +13194,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>DEEP FLY S.A</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>76.419.925-1</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -13224,7 +13224,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>7088.13</v>
+        <v>3669.66</v>
       </c>
     </row>
     <row r="206">
@@ -13982,7 +13982,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>3949-279-CM26</t>
+          <t>418-2204-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14007,12 +14007,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -14022,22 +14022,26 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>AVA COMERCIAL SPA</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
-        </is>
-      </c>
-      <c r="K218" t="inlineStr"/>
+          <t>78.203.286-0</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>4432.84</v>
+        <v>4402.09</v>
       </c>
     </row>
     <row r="219">
@@ -14104,7 +14108,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>418-2204-CM26</t>
+          <t>3949-279-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14129,12 +14133,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14144,26 +14148,22 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>AVA COMERCIAL SPA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>78.203.286-0</t>
-        </is>
-      </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>4402.09</v>
+        <v>4432.84</v>
       </c>
     </row>
     <row r="221">
@@ -14230,7 +14230,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1274667-235-CM26</t>
+          <t>1274667-237-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14270,32 +14270,28 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>1287.95</v>
+        <v>10073.66</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1274667-237-CM26</t>
+          <t>1274667-258-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14335,12 +14331,12 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
@@ -14350,13 +14346,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>10073.66</v>
+        <v>778.34</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1274667-258-CM26</t>
+          <t>1274667-263-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14396,28 +14392,32 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
-        </is>
-      </c>
-      <c r="K224" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>778.34</v>
+        <v>894.38</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1274667-263-CM26</t>
+          <t>1692-459-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14442,12 +14442,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -14476,13 +14476,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>894.38</v>
+        <v>984.4</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1692-459-CM26</t>
+          <t>1692-460-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14522,32 +14522,28 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
-        </is>
-      </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>984.4</v>
+        <v>1282.71</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1692-460-CM26</t>
+          <t>1274667-235-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14572,12 +14568,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14587,22 +14583,26 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
-        </is>
-      </c>
-      <c r="K227" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>1282.71</v>
+        <v>1287.95</v>
       </c>
     </row>
     <row r="228">
@@ -14669,7 +14669,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>4778-406-CM26</t>
+          <t>4778-407-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14709,28 +14709,32 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
-        </is>
-      </c>
-      <c r="K229" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>3687.42</v>
+        <v>13687.9</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>4778-407-CM26</t>
+          <t>4778-406-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14770,26 +14774,22 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr"/>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>13687.9</v>
+        <v>3687.42</v>
       </c>
     </row>
     <row r="231">
@@ -15299,7 +15299,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>3950-1221-CM26</t>
+          <t>3949-324-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15324,12 +15324,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15339,12 +15339,12 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K239" t="inlineStr"/>
@@ -15354,7 +15354,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>3601.05</v>
+        <v>783.11</v>
       </c>
     </row>
     <row r="240">
@@ -15421,7 +15421,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>3949-324-CM26</t>
+          <t>3950-1221-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15446,12 +15446,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15461,12 +15461,12 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
@@ -15476,13 +15476,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>783.11</v>
+        <v>3601.05</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>418-2651-CM26</t>
+          <t>5019-212-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15507,12 +15507,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>65.224.300-2</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15522,28 +15522,32 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
-        </is>
-      </c>
-      <c r="K242" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>4575.76</v>
+        <v>1546.41</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>5019-212-CM26</t>
+          <t>418-2651-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15568,12 +15572,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>65.224.300-2</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15583,26 +15587,22 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K243" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr"/>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>1546.41</v>
+        <v>4575.76</v>
       </c>
     </row>
     <row r="244">
@@ -16055,7 +16055,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>418-2753-CM26</t>
+          <t>418-2763-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16075,7 +16075,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -16114,13 +16114,13 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>1274.88</v>
+        <v>3054.33</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>418-2763-CM26</t>
+          <t>418-2753-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -16140,7 +16140,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -16179,7 +16179,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>3054.33</v>
+        <v>1274.88</v>
       </c>
     </row>
     <row r="253">
@@ -16311,7 +16311,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>1426103-82-CM26</t>
+          <t>3765-780-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16336,12 +16336,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -16351,32 +16351,28 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K255" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr"/>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>1878.69</v>
+        <v>2447.53</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>3765-780-CM26</t>
+          <t>1426103-82-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16401,12 +16397,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16416,22 +16412,26 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
-        </is>
-      </c>
-      <c r="K256" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>2447.53</v>
+        <v>1878.69</v>
       </c>
     </row>
     <row r="257">
@@ -16498,7 +16498,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>3949-368-CM26</t>
+          <t>2713-1004-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16553,13 +16553,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>2940.69</v>
+        <v>2386.82</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2713-1004-CM26</t>
+          <t>3949-368-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16584,12 +16584,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16614,7 +16614,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>2386.82</v>
+        <v>2940.69</v>
       </c>
     </row>
     <row r="260">
@@ -16803,7 +16803,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>3950-1463-CM26</t>
+          <t>886182-303-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -16823,17 +16823,17 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -16843,12 +16843,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K263" t="inlineStr"/>
@@ -16858,7 +16858,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>7710.47</v>
+        <v>2282.11</v>
       </c>
     </row>
     <row r="264">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -16925,7 +16925,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>886182-303-CM26</t>
+          <t>3950-1463-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -16945,17 +16945,17 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE AYSEN</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16965,12 +16965,12 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K265" t="inlineStr"/>
@@ -16980,7 +16980,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>2282.11</v>
+        <v>7710.47</v>
       </c>
     </row>
     <row r="266">
@@ -17006,7 +17006,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -17132,7 +17132,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -17177,66 +17177,692 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
+          <t>1403-779-CM26</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>61.004.101-9</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M269" s="2" t="n">
+        <v>756.21</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
           <t>4778-575-CM26</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr">
+      <c r="B270" t="inlineStr">
         <is>
           <t>2239-8-LR25</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr">
+      <c r="C270" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr">
+      <c r="D270" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr">
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M270" s="2" t="n">
+        <v>1644.47</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>1403-790-CM26</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>61.004.101-9</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M271" s="2" t="n">
+        <v>1050.27</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>1274667-327-CM26</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>62.000.940-7</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M272" s="2" t="n">
+        <v>1034.95</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>1403-799-CM26</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>61.004.101-9</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M273" s="2" t="n">
+        <v>870.41</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>707426-135-CM26</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F269" t="inlineStr">
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M274" s="2" t="n">
+        <v>15035.27</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2713-1132-CM26</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M275" s="2" t="n">
+        <v>3962.27</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>3949-416-CM26</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>61.974.500-0</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M276" s="2" t="n">
+        <v>1500.41</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>3950-1583-CM26</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>61.974.600-7</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>DIRECCION SALUD RURAL</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M277" s="2" t="n">
+        <v>1410.54</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2495-453-CM26</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>69.240.300-2</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M278" s="2" t="n">
+        <v>2957.3</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>4778-579-CM26</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
         <is>
           <t>61.602.280-6</t>
         </is>
       </c>
-      <c r="G269" t="inlineStr">
+      <c r="G279" t="inlineStr">
         <is>
           <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
-      <c r="H269" t="inlineStr">
-        <is>
-          <t>Aysén</t>
-        </is>
-      </c>
-      <c r="I269" t="inlineStr">
-        <is>
-          <t>EVENTAIL SPA</t>
-        </is>
-      </c>
-      <c r="J269" t="inlineStr">
-        <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L269" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M269" s="2" t="n">
-        <v>1644.47</v>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M279" s="2" t="n">
+        <v>28432.24</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/aysen.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/aysen.xlsx
@@ -11457,7 +11457,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -13750,7 +13750,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -13876,7 +13876,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -15071,7 +15071,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -15949,7 +15949,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/aysen.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M279"/>
+  <dimension ref="A1:M280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9185,7 +9185,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2713-185-CM26</t>
+          <t>418-218-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9210,12 +9210,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9225,28 +9225,32 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr"/>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1218.42</v>
+        <v>1010.65</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>418-218-CM26</t>
+          <t>2713-185-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9271,12 +9275,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9286,32 +9290,28 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>1010.65</v>
+        <v>1218.42</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>707426-13-CM26</t>
+          <t>1428-8-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9336,12 +9336,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.701.004-8</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9351,17 +9351,17 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -9370,13 +9370,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>18627.31</v>
+        <v>2458.31</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1428-8-CM26</t>
+          <t>707426-13-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9401,12 +9401,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>60.701.004-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9416,17 +9416,17 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -9435,13 +9435,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>2458.31</v>
+        <v>18627.31</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2713-211-CM26</t>
+          <t>951405-33-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9500,13 +9500,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>5179.77</v>
+        <v>13609.08</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>951405-33-CM26</t>
+          <t>2713-211-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>13609.08</v>
+        <v>5179.77</v>
       </c>
     </row>
     <row r="147">
@@ -11254,7 +11254,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>4778-217-CM26</t>
+          <t>2500-70-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11279,12 +11279,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11294,12 +11294,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.475.342-9</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -11309,13 +11309,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>27589.6</v>
+        <v>938.6900000000001</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2500-70-CM26</t>
+          <t>4778-217-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11355,12 +11355,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Equilibrium SpA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -11370,7 +11370,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>938.6900000000001</v>
+        <v>27589.6</v>
       </c>
     </row>
     <row r="176">
@@ -11437,7 +11437,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>611136-13-CM26</t>
+          <t>4778-236-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>61.979.930-5</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11477,32 +11477,28 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.888.569-9</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>1109.81</v>
+        <v>1328.61</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>4778-236-CM26</t>
+          <t>611136-13-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11527,12 +11523,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.979.930-5</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11542,22 +11538,26 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rodolfo </t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>76.888.569-9</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr"/>
+          <t>77.806.000-0</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>1328.61</v>
+        <v>1109.81</v>
       </c>
     </row>
     <row r="179">
@@ -11689,7 +11689,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>418-1399-CM26</t>
+          <t>418-1467-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11744,13 +11744,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>2369.79</v>
+        <v>1621.8</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>418-1467-CM26</t>
+          <t>418-1399-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11805,7 +11805,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>1621.8</v>
+        <v>2369.79</v>
       </c>
     </row>
     <row r="183">
@@ -12364,7 +12364,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>4778-309-CM26</t>
+          <t>854-90-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12404,12 +12404,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rodolfo </t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>76.888.569-9</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -12419,13 +12419,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>3388.59</v>
+        <v>4291.54</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>854-90-CM26</t>
+          <t>4778-309-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12450,12 +12450,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12465,12 +12465,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t xml:space="preserve">Rodolfo </t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>76.888.569-9</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -12480,13 +12480,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>4291.54</v>
+        <v>3388.59</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>418-1750-CM26</t>
+          <t>418-1749-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12526,12 +12526,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>AVA COMERCIAL SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>78.203.286-0</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -12545,13 +12545,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>2907.26</v>
+        <v>1879.87</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>418-1749-CM26</t>
+          <t>418-1750-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12591,12 +12591,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>AVA COMERCIAL SPA</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>78.203.286-0</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -12610,7 +12610,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>1879.87</v>
+        <v>2907.26</v>
       </c>
     </row>
     <row r="196">
@@ -12681,7 +12681,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>707426-91-CM26</t>
+          <t>4778-313-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12706,12 +12706,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12721,12 +12721,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>CORCORAN Y COMPAÑIA SPA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>86.527.400-9</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
@@ -12736,7 +12736,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>11635.88</v>
+        <v>8296.370000000001</v>
       </c>
     </row>
     <row r="198">
@@ -12803,7 +12803,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>4778-313-CM26</t>
+          <t>707426-91-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>CORCORAN Y COMPAÑIA SPA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>86.527.400-9</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -12858,13 +12858,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>8296.370000000001</v>
+        <v>11635.88</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>3950-854-CM26</t>
+          <t>3950-855-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12904,12 +12904,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K200" t="inlineStr"/>
@@ -12919,13 +12919,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>8185</v>
+        <v>3669.66</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>3950-838-CM26</t>
+          <t>3950-854-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12980,13 +12980,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>2438.42</v>
+        <v>8185</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>3951-130-CM26</t>
+          <t>3950-838-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -13011,12 +13011,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>61.974.700-3</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -13041,13 +13041,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>4200.73</v>
+        <v>2438.42</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1691-1199-CM26</t>
+          <t>3951-130-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13072,12 +13072,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.974.700-3</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -13087,12 +13087,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>DEEP FLY S.A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>76.419.925-1</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
@@ -13102,7 +13102,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>7088.13</v>
+        <v>4200.73</v>
       </c>
     </row>
     <row r="204">
@@ -13169,7 +13169,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>3950-855-CM26</t>
+          <t>1691-1199-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13194,12 +13194,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DEEP FLY S.A</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>76.419.925-1</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -13224,7 +13224,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>3669.66</v>
+        <v>7088.13</v>
       </c>
     </row>
     <row r="206">
@@ -13982,7 +13982,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>418-2204-CM26</t>
+          <t>1079689-279-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14007,12 +14007,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -14022,32 +14022,28 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>AVA COMERCIAL SPA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>78.203.286-0</t>
-        </is>
-      </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>4402.09</v>
+        <v>2171.24</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>418-2205-CM26</t>
+          <t>418-2204-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14087,28 +14083,32 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>AVA COMERCIAL SPA</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
-        </is>
-      </c>
-      <c r="K219" t="inlineStr"/>
+          <t>78.203.286-0</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>2021.76</v>
+        <v>4402.09</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>3949-279-CM26</t>
+          <t>418-2205-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14133,12 +14133,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14163,13 +14163,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>4432.84</v>
+        <v>2021.76</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1079689-279-CM26</t>
+          <t>3949-279-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14194,12 +14194,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14209,12 +14209,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -14224,7 +14224,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>2171.24</v>
+        <v>4432.84</v>
       </c>
     </row>
     <row r="222">
@@ -14291,7 +14291,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1274667-258-CM26</t>
+          <t>1692-460-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14316,12 +14316,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14331,12 +14331,12 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
@@ -14346,13 +14346,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>778.34</v>
+        <v>1282.71</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1274667-263-CM26</t>
+          <t>1692-459-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14377,12 +14377,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -14411,13 +14411,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>894.38</v>
+        <v>984.4</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1692-459-CM26</t>
+          <t>1274667-263-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14442,12 +14442,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -14476,13 +14476,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>984.4</v>
+        <v>894.38</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1692-460-CM26</t>
+          <t>1274667-258-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14507,12 +14507,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14522,12 +14522,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K226" t="inlineStr"/>
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>1282.71</v>
+        <v>778.34</v>
       </c>
     </row>
     <row r="227">
@@ -14608,7 +14608,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>4778-405-CM26</t>
+          <t>4778-407-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14648,28 +14648,32 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
-        </is>
-      </c>
-      <c r="K228" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>34317.57</v>
+        <v>13687.9</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>4778-407-CM26</t>
+          <t>4778-405-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14709,26 +14713,22 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>13687.9</v>
+        <v>34317.57</v>
       </c>
     </row>
     <row r="230">
@@ -15299,7 +15299,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>3949-324-CM26</t>
+          <t>3950-1221-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15324,12 +15324,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15339,12 +15339,12 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>76.025.795-8</t>
         </is>
       </c>
       <c r="K239" t="inlineStr"/>
@@ -15354,7 +15354,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>783.11</v>
+        <v>3601.05</v>
       </c>
     </row>
     <row r="240">
@@ -15421,7 +15421,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>3950-1221-CM26</t>
+          <t>3949-324-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15446,12 +15446,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15461,12 +15461,12 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
@@ -15476,13 +15476,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>3601.05</v>
+        <v>783.11</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>5019-212-CM26</t>
+          <t>418-2651-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15507,12 +15507,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>65.224.300-2</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15522,32 +15522,28 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr"/>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>1546.41</v>
+        <v>4575.76</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>418-2651-CM26</t>
+          <t>5019-212-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15572,12 +15568,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>65.224.300-2</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15587,22 +15583,26 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
-        </is>
-      </c>
-      <c r="K243" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>4575.76</v>
+        <v>1546.41</v>
       </c>
     </row>
     <row r="244">
@@ -15738,7 +15738,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2151-315-CM26</t>
+          <t>418-2658-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15763,12 +15763,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15778,32 +15778,28 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K246" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr"/>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>1524.83</v>
+        <v>4912.07</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>418-2658-CM26</t>
+          <t>2151-315-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15828,12 +15824,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15843,22 +15839,26 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
-        </is>
-      </c>
-      <c r="K247" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>4912.07</v>
+        <v>1524.83</v>
       </c>
     </row>
     <row r="248">
@@ -15929,7 +15929,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1274667-321-CM26</t>
+          <t>697209-32-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15949,17 +15949,17 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -15969,32 +15969,28 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA INVERNET SPA</t>
+          <t xml:space="preserve">Comercial sotocopias ltda </t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>77.884.798-1</t>
-        </is>
-      </c>
-      <c r="K249" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.025.795-8</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr"/>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>1091.44</v>
+        <v>1453.52</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>697209-32-CM26</t>
+          <t>1274667-321-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -16014,17 +16010,17 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -16034,22 +16030,26 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial sotocopias ltda </t>
+          <t>COMERCIALIZADORA INVERNET SPA</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>76.025.795-8</t>
-        </is>
-      </c>
-      <c r="K250" t="inlineStr"/>
+          <t>77.884.798-1</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>1453.52</v>
+        <v>1091.44</v>
       </c>
     </row>
     <row r="251">
@@ -16498,7 +16498,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2713-1004-CM26</t>
+          <t>3949-368-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16553,13 +16553,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>2386.82</v>
+        <v>2940.69</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>3949-368-CM26</t>
+          <t>2713-1004-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16584,12 +16584,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16614,7 +16614,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>2940.69</v>
+        <v>2386.82</v>
       </c>
     </row>
     <row r="260">
@@ -17746,7 +17746,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2495-453-CM26</t>
+          <t>2713-1183-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17761,7 +17761,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -17771,12 +17771,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17786,28 +17786,32 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
-        </is>
-      </c>
-      <c r="K278" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>2957.3</v>
+        <v>2751.18</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>4778-579-CM26</t>
+          <t>2495-453-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -17822,7 +17826,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -17832,12 +17836,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -17862,6 +17866,67 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
+        <v>2957.3</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>4778-579-CM26</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M280" s="2" t="n">
         <v>28432.24</v>
       </c>
     </row>
